--- a/exercisesLifeContingencies/lifeInsurance/makeham_comm.xlsx
+++ b/exercisesLifeContingencies/lifeInsurance/makeham_comm.xlsx
@@ -1,37 +1,81 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="makeham" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="makeham" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>lx</t>
+  </si>
+  <si>
+    <t>dx</t>
+  </si>
+  <si>
+    <t>qx</t>
+  </si>
+  <si>
+    <t>px</t>
+  </si>
+  <si>
+    <t>exo</t>
+  </si>
+  <si>
+    <t>Dx</t>
+  </si>
+  <si>
+    <t>Nx</t>
+  </si>
+  <si>
+    <t>Sx</t>
+  </si>
+  <si>
+    <t>Cx</t>
+  </si>
+  <si>
+    <t>Mx</t>
+  </si>
+  <si>
+    <t>Rx</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +90,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,5017 +406,4989 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L131"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lx</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dx</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>qx</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>exo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Dx</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Nx</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Sx</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Cx</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Mx</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>100000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>22.28393070392576</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.0002228393070392576</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.9997771606929607</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>85.56426560366678</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>100000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>2055241.875593928</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>40188846.29433698</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>21.22279114659596</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>2131.339257431903</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>141487.2901493073</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:12">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>99977.71606929608</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>22.31446446393932</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.0002231943811206172</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.9997768056188794</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>84.5832254906758</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>95216.87244694863</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>1955241.875593928</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>38133604.41874305</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>20.23987706479757</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>2110.116466285307</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>139355.9508918754</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:12">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>99955.40160483214</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>22.34937651317246</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.0002235934842373943</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.9997764065157626</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>83.60199658375426</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>90662.49578669581</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>1860025.003146979</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>36178362.54314913</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>19.30623173581466</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>2089.876589220509</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>137245.8344255901</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:12">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>99933.05222831896</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>22.38920847730267</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.0002240420759505035</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.9997759579240495</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>82.62058180425171</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>86325.92785083161</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>1769362.507360283</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>34318337.54000215</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>18.41965722290829</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>2070.570357484694</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>135155.9578363696</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>99910.66301984167</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>22.43456899188494</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.0002245462927958908</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.9997754537072041</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>81.63898439283155</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>82196.74972452149</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>1683036.579509452</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>32548975.03264187</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>17.57807183858377</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>2052.150700261786</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>133085.3874788849</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:12">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>99888.22845084978</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>22.48614199029288</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.0002251130322263872</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.9997748869677736</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>80.65720794300881</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>78265.04071341998</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1600839.82978493</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>30865938.45313241</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>16.77950536411392</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2034.572628423202</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>131033.2367786231</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>99865.7423088595</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>22.54469601619907</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.0002257500469627916</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.9997742499530372</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>79.67525643809513</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>74521.35450741681</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>1522574.789071511</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>29265098.62334748</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>16.0220945521716</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2017.793123059088</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>128998.6641501999</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:12">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>99843.1976128433</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>22.61109468680176</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.0002264660510421512</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.9997735339489578</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>78.69313429188064</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>70956.69648394002</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>1448053.434564094</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>27742523.83427597</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>15.30407890258514</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>2001.771028506917</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>126980.8710271408</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:12">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>99820.5865181565</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>22.68630844897002</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.0002272708390151923</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.9997727291609848</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>77.71084639341203</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>67562.50209627839</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>1377096.738080154</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>26294470.39971188</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>14.62379670227322</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>1986.466949604332</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>124979.0999986339</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:12">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>99797.90020970753</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>22.77142778784285</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.000228175419923593</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.9997718245800764</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>76.72839815625679</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>64330.61629499143</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>1309534.235983875</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>24917373.66163172</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>13.97968132100305</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>1971.843152902059</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>122992.6330490295</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:12">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>99775.12878191969</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>22.86767806680746</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.0002291921678877484</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.9997708078321123</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>75.745795572679</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>61253.27393295654</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>1245203.619688884</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>23607839.42564785</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>13.3702577551585</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>1957.863471581055</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>121020.7898961275</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:12">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>99752.26110385288</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>22.97643619998853</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.0002303349913649333</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.9997696650086351</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>74.76304527318699</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>58323.08110696536</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>1183950.345755927</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>22362635.80595896</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>12.79413941252302</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>1944.493213825897</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>119062.9264245464</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:12">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>99729.2846676529</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>23.09924938315849</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>0.0002316195233941221</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.9997683804766059</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>73.78015459195352</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>55532.99739103068</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>1125627.264648962</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>21178685.46020303</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>12.25002513176909</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>1931.699074413374</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>117118.4332107205</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:12">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>99706.18541826974</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>23.23785613606873</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>0.0002330633354248324</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.9997669366645752</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>72.79713163864982</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>52876.31891870697</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1070094.267257931</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>20053058.19555407</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>11.73669643064858</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>1919.449049281605</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>115186.7341363072</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:12">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>99682.94756213368</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>23.39420994107155</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.0002346861776583165</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.9997653138223417</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>71.81398537727971</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>50346.66227376646</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>1017217.948339224</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>18982963.92829614</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>11.25301497798516</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>1907.712352850956</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>113267.2850870255</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:12">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>99659.5533521926</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>23.57050579692938</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>0.0002365102491843629</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.9997634897508156</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>70.83072571264681</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>47937.94915051388</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>966871.2860654577</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>17965745.97995692</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>10.79792028473843</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>1896.459337872971</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>111359.5727341746</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:12">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>99635.98284639567</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>23.76921004595136</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>0.000238560501607088</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.9997614394983929</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>69.84736358513778</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>45644.39174687133</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>918933.3369149438</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>16998874.69389146</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>10.37042761017529</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>1885.661417588233</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>109463.1133963016</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:12">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>99612.21363634971</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>23.99309387628278</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>0.0002408649803112839</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.9997591350196887</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>68.86391107455717</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>43460.47885512443</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>873288.9451680725</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>16079941.35697652</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>9.969626079770013</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>1875.290989978057</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>107577.4519787134</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:12">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>99588.22054247343</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>24.24527094990752</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>0.000243455208034038</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.999756544791966</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>67.88038151380417</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>41380.96261689586</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>829828.466312948</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>15206652.41180845</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>9.594677011947743</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>1865.321363898287</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>105702.1609887353</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:12">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>99563.97527152352</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>24.52923966152514</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>0.0002463666159836508</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.9997536333840163</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>66.89678961324029</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>39400.84591050792</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>788447.5036960521</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>14376823.9454955</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>9.244812451300099</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>1855.72668688634</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>103836.839624837</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:12">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>99539.446031862</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>24.84893059472741</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>0.000249639028398585</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.9997503609716014</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>65.91315159665596</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>37515.37034041338</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>749046.6577855442</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>13588376.44179945</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>8.919333906470371</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>1846.48187443504</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>101981.1129379507</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:12">
+      <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>99514.59710126727</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>25.20875981004588</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>0.0002533172071670364</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.999746682792833</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>64.92948534980732</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>35720.00479982056</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>711531.2874451309</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>12839329.7840139</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>8.617611291317791</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>1837.562540528569</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>100134.6310635157</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:12">
+      <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>99489.38834145722</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>25.61368867592734</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>0.0002574514639492875</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.9997425485360507</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>63.94581058255771</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>34010.43457901398</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>675811.2826453103</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>12127798.49656877</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>8.339082068493923</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>1828.944929237251</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>98297.0685229871</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:12">
+      <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>99463.77465278129</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>26.06929103873174</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>0.0002620983481648187</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.9997379016518352</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>62.96214900572461</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>32382.55099318291</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>641800.8480662962</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>11451987.21392346</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>8.083250594929762</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>1820.605847168757</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>96468.12359374984</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:12">
+      <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>99437.70536174256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>26.58182862274045</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>0.0002673214202403296</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.9997326785797597</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>61.97852452379806</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>30832.44150481737</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>609418.2970731134</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>10810186.36585717</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>7.849687669090152</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>1812.522596573828</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>94647.51774658108</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:12">
+      <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>99411.12353311981</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>27.15833565723852</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>0.0002731921206804433</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.9997268078793196</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>60.99496344476375</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>29356.38031691887</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>578585.855568296</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>10200768.06878405</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>7.638030280267325</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>1804.672908904737</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>92834.99515000726</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:12">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>99383.96519746257</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>27.80671384487818</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>0.0002797907468234939</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.9997202092531765</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>60.01149470832866</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>27950.81941440437</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>549229.4752513771</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>9622182.213215755</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>7.447981560271249</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>1797.03487862447</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>91030.32224110252</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:12">
+      <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>99356.15848361769</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>28.53583891695504</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>0.0002872075506186178</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.9997127924493814</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>59.02815013391166</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>26612.38003215818</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>521278.6558369728</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>9072952.737964377</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>7.279310938255203</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>1789.586897064199</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>89233.28736247805</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:12">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>99327.62264470074</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>29.35568016571148</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>0.0002955439724025011</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.9997044560275975</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>58.04496468982128</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>25337.84452921239</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>494666.2758048146</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>8551674.082127405</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>7.131854499314675</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>1782.307586125944</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>87443.70046541386</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:12">
+      <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>99298.26696453503</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>30.27743450465336</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>0.0003049140275073192</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.9996950859724927</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>57.06197678509969</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>24124.14864951248</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>469328.4312756023</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>8057007.80632259</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>7.005515547531529</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>1775.175731626629</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>85661.39287928792</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:12">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>99267.98953003038</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>31.3136767854815</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>0.0003154458646108527</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>0.9996845541353891</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>56.07922858556097</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>22968.37415065483</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>445204.2826260898</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>7587679.375046989</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>6.90026537396083</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>1768.170216079097</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>83886.21714766129</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:12">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>99236.67585324489</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>32.47852829574072</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>0.0003272835170715638</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>0.9996727164829284</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>55.09676635559358</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>21867.74178286874</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>422235.9084754349</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>7142475.092420898</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>6.816144229628636</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>1761.269950705137</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>82118.04693158218</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:12">
+      <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>99204.19732494914</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>33.78784557659677</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>0.0003405888711132121</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>0.9996594111288868</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>54.11464082732714</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>20819.60460135964</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>400368.1666925661</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>6720239.183945464</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>6.75326250304811</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>1754.453806475508</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>80356.77698087705</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:12">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>99170.40947937254</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>35.259431935956</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>0.000355543877665343</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>0.9996444561223347</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>53.13290759878074</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>19821.4415959347</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>379548.5620912065</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>6319871.017252898</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>6.711802100891188</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>1747.70054397246</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>78602.32317440154</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:12">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>99135.15004743657</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>36.91327428958848</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>0.0003723530379681206</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>0.9996276469620319</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>52.15162756260975</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>18870.85162259882</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>359727.1204952718</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>5940322.455161691</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>6.692018029257436</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>1740.988741871569</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>76854.62263042908</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:12">
+      <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>99098.23677314699</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>38.77180824259952</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>0.0003912461967547909</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>0.9996087538032452</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>51.17086736704832</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>17965.54762254105</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>340856.268872673</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>5580595.33466642</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37">
         <v>6.694240171367866</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>1734.296723842311</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>75113.63388855751</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:12">
+      <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>99059.46496490439</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>40.86021462610606</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>0.000412481680984067</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>0.9995875183190159</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>50.19069991059919</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>17103.35111462963</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>322890.721250132</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>5239739.065793746</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>6.718875255450614</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38">
         <v>1727.602483670943</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>73379.33716471519</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:12">
+      <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>99018.60475027827</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>43.20675102869054</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>0.0004363498267588861</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>0.9995636501732411</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>49.2112048719485</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>16282.18694820134</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>305787.3701355023</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>4916848.344543614</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>6.766409003908047</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>1720.883608415493</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>71651.73468104425</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:12">
+      <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>98975.39799924959</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>45.84312220818751</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>0.0004631769422996923</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>0.9995368230577003</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>48.23246927647482</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>15500.07830356879</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>289505.183187301</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>4611060.974408112</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>6.837408451478852</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>1714.117199411585</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>69930.85107262876</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:12">
+      <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>98929.5548770414</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>48.80489363396037</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>0.0004933297607031539</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>0.9995066702392968</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>47.25458810057203</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>14755.14192828071</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>274005.1048837322</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>4321555.79122081</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>6.932524415828374</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>1707.279790960106</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41">
         <v>68216.73387321718</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:12">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>98880.74998340744</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>52.13195279015003</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>0.0005272204427949623</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>0.999472779557205</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>46.27766491481071</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>14045.58359775627</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>259249.9629554515</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>4047550.686337078</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>7.052494098783542</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>1700.347266544277</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>66509.45408225707</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:12">
+      <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>98828.61803061729</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>55.86902325921151</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>0.0005653121977472475</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>0.9994346878022528</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>45.30181256671293</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>13369.69378947862</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>245204.3793576952</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>3788300.723381627</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>7.198143789845601</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>1693.294772445494</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>64809.1068157128</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:12">
+      <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>98772.74900735808</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>60.06623699527086</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>0.0006081255973831023</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>0.9993918744026169</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>44.32715390360494</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>12725.8435604755</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>231834.6855682167</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>3543096.344023932</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44">
         <v>7.370391635636258</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>1686.096628655648</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>63115.8120432673</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:12">
+      <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>98712.68277036281</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>64.7797705755454</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>0.0006562456693254282</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>0.9993437543306746</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>43.35382253563195</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>12112.48061834103</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>219108.8420077412</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>3311261.658455715</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45">
         <v>7.570250429118558</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45">
         <v>1678.726237020012</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>61429.71541461165</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:12">
+      <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>98647.90299978726</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>70.07255156888313</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>0.0007103298644780542</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>0.9992896701355219</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>42.38196363856191</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>11528.12557656234</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>206996.3613894001</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>3092152.816447974</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>7.798830360462397</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>1671.155986590893</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46">
         <v>59750.98917759164</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:12">
+      <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>98577.83044821837</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>76.01504146213773</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>0.0007711170058877226</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>0.9992288829941123</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>41.41173479545921</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>10971.36838541319</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>195468.2358128378</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>2885156.455058574</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>8.05734165700099</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>1663.357156230431</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>58079.83319100074</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:12">
+      <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>98501.81540675624</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>82.68610180573953</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>0.0008394373389393195</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>0.9991605626610607</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>40.44330687566832</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>10440.86493016509</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>184496.8674274246</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>2689688.219245736</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>8.347097022097758</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>1655.29981457343</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48">
         <v>56416.47603477031</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:12">
+      <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>98419.1293049505</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>90.17395034379679</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>0.000916223817266193</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>0.9990837761827338</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>39.47686494880007</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>9935.333788849415</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>174056.0024972595</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>2505191.351818311</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>8.669513761746094</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>1646.952717551332</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>54761.17622019689</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:12">
+      <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>98328.9553546067</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>98.57721382670125</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>0.001002524774835645</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>0.9989974752251644</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>38.51260923055081</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>9453.553142285315</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>164120.6687084101</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>2331135.349321052</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50">
         <v>9.026115462253701</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50">
         <v>1638.283203789586</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>53114.22350264556</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:12">
+      <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>98230.37814078</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>108.006083903227</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>0.001099518152606893</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>0.9989004818473931</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>37.55075605619838</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>8994.357829571378</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>154667.1155661248</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>2167014.680612641</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>9.418533052053014</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>1629.257088327333</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>51475.94029885596</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:12">
+      <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>98122.37205687677</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>118.5835818678643</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>0.001208527468120391</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>0.9987914725318796</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>36.59153887650121</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>8556.636542730212</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>145672.7577365534</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>2012347.565046517</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52">
         <v>9.848505044392528</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>1619.83855527528</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52">
         <v>49846.68321052863</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:12">
+      <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>98003.78847500891</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>130.4469369913162</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>0.001331039738576845</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>0.9986689602614232</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>35.63520926946964</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>8139.329154698667</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>137116.1211938232</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>1866674.807309964</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>10.31787671453429</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>1609.990050230887</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>48226.84465525336</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:12">
+      <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>97873.3415380176</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>143.7490815514412</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>0.001468725592613018</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>0.998531274407387</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>34.68203796007863</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>7741.424175379433</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>128976.7920391245</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>1729558.68611614</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>10.82859791395515</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>1599.672173516353</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>46616.85460502247</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:12">
+      <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>97729.59245646615</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>158.6602633374356</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>0.001623461833304085</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>0.9983765381666959</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>33.73231583844497</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>7361.956331018837</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>121235.3678637451</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>1600581.894077016</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55">
         <v>11.38271916367662</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>1588.843575602398</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55">
         <v>45017.18243150611</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:12">
+      <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>97570.93219312871</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>175.3697731078956</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>0.001797356745150025</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>0.99820264325485</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>32.78635496530094</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>7000.004262759025</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>113873.4115327262</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>1479346.526213271</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>11.98238559785606</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>1577.460856438721</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56">
         <v>43428.33885590371</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:12">
+      <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>97395.56242002081</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>194.0877799782701</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>0.00199277847117163</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>0.9980072215288284</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>31.84448955176525</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>6654.68834083931</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>106873.4072699672</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>1365473.114680544</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57">
         <v>12.6298282456966</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>1565.478470840865</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>41850.877999465</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:12">
+      <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>97201.47464004254</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>215.0472616677226</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>0.00221238682297864</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>0.9977876131770214</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>30.90707689845091</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>6325.168591601264</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>100218.7189291279</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>1258599.707410577</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>13.32735204302571</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58">
         <v>1552.848642595168</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58">
         <v>40285.39952862413</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:12">
+      <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>96986.42737837481</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>238.5060085499472</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>0.002459168927003152</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>0.9975408310729968</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>29.97449827687556</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>6010.642735196273</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>93893.55033752663</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>1158380.988481449</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>14.07731985305896</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K59">
         <v>1539.521290552143</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59">
         <v>38732.55088602896</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:12">
+      <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>96747.92136982486</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>264.7486700409052</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>0.002736479154202054</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>0.9972635208457979</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>29.04715973397454</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>5710.34433271482</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>87882.90760233036</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>1064487.438143923</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>14.88213164741899</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>1525.443970699084</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>37193.02959547682</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:12">
+      <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>96483.17269978396</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>294.0887984360795</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>0.003048083828577686</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>0.9969519161714223</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>28.12549279829583</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>5423.541042366695</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>82172.56326961555</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>976604.5305415925</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>15.74419785225265</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>1510.561839051665</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>35667.58562477773</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:12">
+      <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>96189.08390134788</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>326.8708281901125</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>0.003398211261948947</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>0.9966017887380511</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>27.2099550642177</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>5149.532985354123</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>76749.02222724885</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>894431.9672719771</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62">
         <v>16.66590569962663</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62">
         <v>1494.817641199412</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>34157.02378572607</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:12">
+      <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>95862.21307315778</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>363.4719070015345</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>0.003791607718508949</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>0.9962083922814911</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>26.30103062833073</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>4887.651223209063</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>71599.48924189471</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>817682.9450447281</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>17.64957724123732</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>1478.151735499785</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>32662.20614452666</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:12">
+      <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>95498.74116615624</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>404.3034679956312</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>0.004233599972717883</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>0.9957664000272821</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>25.39923035002934</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>4637.256349624536</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>66711.83801868567</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>746083.4558028334</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>18.69741748119644</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>1460.502158258548</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>31184.05440902687</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:12">
+      <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>95094.4376981606</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>449.8123987439124</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>0.004730165187701751</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>0.9952698348122982</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>24.50509190644226</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>4397.737201208837</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>62074.58166906112</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>679371.6177841477</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>19.81145087030379</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K65">
         <v>1441.804740777352</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65">
         <v>29723.55225076833</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:12">
+      <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>94644.62529941669</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>500.4816216792419</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>0.00528800890801695</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>0.994711991091983</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>23.61917961019031</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>4168.509693138112</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>57676.84446785228</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>617297.0361150866</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66">
         <v>20.99344418139937</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66">
         <v>1421.993289907048</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>28281.74750999097</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:12">
+      <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>94144.14367773745</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>556.8298504742046</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>0.005914652029554546</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>0.9940853479704455</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>22.74208395719685</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>3949.015787378708</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>53508.33477471417</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>559620.1916472343</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>22.24481356339278</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>1400.999845725649</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>26859.75422008392</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:12">
+      <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>93587.31382726325</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>619.4102269918658</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>0.006618527679244313</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>0.9933814723207557</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>21.87442087101169</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>3738.722602987757</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>49559.31898733546</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>506111.8568725202</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68">
         <v>23.56651336465792</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K68">
         <v>1378.755032162256</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>25458.75437435828</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:12">
+      <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>92967.90360027138</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>688.8074725005456</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>0.00740908900626791</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>0.9925909109937321</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>21.01683060997341</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>3537.121679957015</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>45820.59638434771</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>456552.5378851847</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69">
         <v>24.95890414552515</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>1355.188518797598</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>24079.99934219602</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:12">
+      <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>92279.09612777084</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>765.6331043484141</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>0.008296928952233218</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>0.9917030710477668</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>20.16997630416844</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>3343.728410099251</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>42283.47470439069</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>410731.941500837</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>26.42159719443545</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70">
         <v>1330.229614652073</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70">
         <v>22724.81082339842</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:12">
+      <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>91513.46302342243</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>850.5181752728965</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>0.009293913126806386</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>0.9907060868731936</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>19.33454209069502</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71">
         <v>3158.081650519137</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71">
         <v>38939.74629429144</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>368448.4667964463</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71">
         <v>27.95327286408208</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>1303.808017457637</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>21394.58120874635</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:12">
+      <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>90662.94484814953</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>944.1028881455758</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>0.01041332696314734</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>0.9895866730368527</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>18.51123081835447</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>2979.743537154143</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>35781.6646437723</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>329508.7205021549</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>29.55147020829645</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>1275.854744593555</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72">
         <v>20090.77319128871</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:12">
+      <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>89718.84196000396</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>1047.022327126771</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>0.01167003835820268</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>0.9883299616417973</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>17.70076129671536</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73">
         <v>2808.299517557555</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>32801.92110661816</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>293727.0558583826</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>31.21234580116072</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73">
         <v>1246.303274385259</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>18814.91844669516</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:12">
+      <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>88671.81963287719</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>1159.887432394665</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>0.01308067700873716</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>0.9869193229912628</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>16.90386506965927</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>2643.358623301272</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>29993.6215890606</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>260925.1347517644</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>32.93040035206101</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>1215.090928584098</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>17568.6151723099</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:12">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>87511.93220048252</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>1283.260238960788</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>0.01466383162493712</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>0.9853361683750629</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>16.12128270013059</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>2484.554002792007</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>27350.26296575933</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>230931.5131627038</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75">
         <v>34.69817291429099</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>1182.160528232037</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>16353.5242437258</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:12">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>86228.67196152173</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>1417.622314800884</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>0.01644026612671801</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>0.983559733873282</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>15.35375956095467</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>2331.543734506668</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>24865.70896296732</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>203581.2501969445</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>36.50590426797293</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>1147.462355317746</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>15171.36371549376</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:12">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>84811.04964672084</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>1563.335290620649</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>0.01843315578727889</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>0.9815668442127211</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>14.60204113629195</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>2184.01193811933</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>22534.16522846066</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>178715.5412339772</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>38.34117361583858</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>1110.956451049773</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>14023.90136017602</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:12">
+      <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>83247.71435610019</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>1720.59240281539</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>0.02066834406354257</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>0.9793316559364574</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>13.86686784953773</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>2041.670196021618</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>20350.15329034133</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>156181.3760055165</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>40.18851626252876</v>
       </c>
-      <c r="K78" t="n">
+      <c r="K78">
         <v>1072.615277433934</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78">
         <v>12912.94490912624</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:12">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>81527.12195328479</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>1889.360113222323</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>0.02317462051837094</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>0.9768253794816291</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>13.14896944616382</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>1904.259289472345</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>18308.48309431971</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>135831.2227151752</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>42.02903466867073</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>1032.426761171406</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79">
         <v>11840.32963169231</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:12">
+      <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>79637.76184006246</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>2069.309177549417</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>0.02598401976320275</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>0.9740159802367973</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>12.44905897395524</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>1771.551241019277</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>16404.22380484736</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>117522.7396208555</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80">
         <v>43.84002138873453</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>990.3977265027349</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80">
         <v>10807.9028705209</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:12">
+      <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>77568.45266251305</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>2259.735076312524</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>0.02913214069312742</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>0.9708678593068726</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>11.76782641805348</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81">
         <v>1643.351636724863</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81">
         <v>14632.67256382809</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>101118.5158160081</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81">
         <v>45.59462008509516</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81">
         <v>946.5577051140004</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81">
         <v>9817.505144018169</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:12">
+      <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>75308.71758620052</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>2459.468578625294</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>0.03265848440202312</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>0.9673415155979769</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>11.10593206381131</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82">
         <v>1519.502176795726</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82">
         <v>12989.32092710322</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>86485.84325218006</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82">
         <v>47.26156013306991</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82">
         <v>900.9630850289052</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82">
         <v>8870.947438904168</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:12">
+      <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>72849.24900757523</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>2666.778471084772</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>0.03660680799616023</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>0.9633931920038398</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>10.46399967622096</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83">
         <v>1399.883370148574</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83">
         <v>11469.8187503075</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>73496.52232507683</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J83">
         <v>48.80501118861577</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>853.7015248958353</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83">
         <v>7969.984353875263</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:12">
+      <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>70182.47053649045</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>2879.270243354999</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>0.04102549000263478</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>0.9589745099973652</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>9.842609600028446</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84">
         <v>1284.41724609574</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84">
         <v>10069.93538015892</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>62026.70357476932</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84">
         <v>50.18461608467856</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84">
         <v>804.8965137072196</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84">
         <v>7116.282828979428</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:12">
+      <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>67303.20029313545</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>3093.786855754113</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>0.04596790111434956</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>0.9540320988856504</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>9.24229189893078</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85">
         <v>1173.069904006503</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85">
         <v>8785.518134063183</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85">
         <v>51956.7681946104</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J85">
         <v>51.3557727119909</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K85">
         <v>754.7118976225411</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85">
         <v>6311.386315272208</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:12">
+      <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>64209.41343738134</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>3306.320656460233</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>0.05149277153395337</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>0.9485072284660466</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>8.663519664738896</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86">
         <v>1065.853659675154</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86">
         <v>7612.44823005668</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>43171.25006054722</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86">
         <v>52.27024665360077</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>703.3561249105501</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86">
         <v>5556.674417649667</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:12">
+      <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>60903.09278092111</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>3511.949016842887</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>0.05766454307133417</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>0.9423354569286658</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>8.10670263730217</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87">
         <v>962.8284768465462</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87">
         <v>6546.594570381525</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>35558.80183049054</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J87">
         <v>52.87720397469023</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87">
         <v>651.0858782569494</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87">
         <v>4853.318292739117</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:12">
+      <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>57391.14376407822</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>3704.810120460977</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>0.0645536902991618</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>0.9354463097008382</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>7.572181282549356</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88">
         <v>864.1022977839252</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88">
         <v>5583.76609353498</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>29012.20726010901</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J88">
         <v>53.1247543980358</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K88">
         <v>598.208674282259</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88">
         <v>4202.232414482168</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:12">
+      <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>53686.33364361724</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>3878.139165823952</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>0.07223699035899844</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>0.9277630096410016</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>7.060221478463134</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89">
         <v>769.8298149199882</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89">
         <v>4719.663795751055</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89">
         <v>23428.44116657403</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J89">
         <v>52.96208468423308</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>545.0839198842233</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89">
         <v>3604.023740199909</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:12">
+      <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>49808.19447779329</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>4024.388317951662</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>0.08079771531862923</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>0.9192022846813708</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>6.571009956520703</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90">
         <v>680.2091676205175</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90">
         <v>3949.833980831067</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>18708.77737082298</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J90">
         <v>52.34223493573745</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>492.1218351999902</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90">
         <v>3058.939820315685</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:12">
+      <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>45783.80615984162</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>4135.454990417877</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>0.09032571420515079</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>0.9096742857948492</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>6.104650638597072</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91">
         <v>595.4760199409459</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91">
         <v>3269.624813210549</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>14758.94338999191</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J91">
         <v>51.2255207554348</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91">
         <v>439.7796002642527</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91">
         <v>2566.817985115695</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:12">
+      <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>41648.35116942375</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>4203.040978083322</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>0.1009173439060175</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>0.8990826560939825</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>5.66116199624119</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92">
         <v>515.8944982359421</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92">
         <v>2674.148793269603</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>11489.31857678136</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92">
         <v>49.58352618828467</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>388.5540795088179</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92">
         <v>2127.038384851443</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:12">
+      <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>37445.31019134042</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>4219.157778535268</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>0.1126751990296234</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>0.8873248009703766</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>5.240475540551064</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93">
         <v>441.7445673697554</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93">
         <v>2158.254295033661</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93">
         <v>8815.169783511756</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93">
         <v>47.40348290346864</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>338.9705533205333</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93">
         <v>1738.484305342625</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:12">
+      <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>33226.15241280515</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>4176.779233632662</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>0.1257075806352757</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>0.8742924193647243</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>4.842435526840782</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94">
         <v>373.3056288772507</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94">
         <v>1716.509727663906</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>6656.915488478096</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94">
         <v>44.69271185113265</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94">
         <v>291.5670704170647</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94">
         <v>1399.513752022091</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:12">
+      <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>29049.37317917249</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>4070.619895601847</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>0.1401276327201565</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>0.8598723672798435</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>4.466799929474476</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95">
         <v>310.8364585081537</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95">
         <v>1343.204098786655</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95">
         <v>4940.405760814191</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J95">
         <v>41.48264485129974</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95">
         <v>246.874358565932</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95">
         <v>1107.946681605027</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:12">
+      <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>24978.75328357064</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>3897.986004901254</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>0.1560520639540921</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>0.8439479360459079</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>4.113242709523528</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96">
         <v>254.5520775374181</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96">
         <v>1032.367640278501</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96">
         <v>3597.201662027536</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96">
         <v>37.83178769858684</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96">
         <v>205.3917137146323</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96">
         <v>861.0723230390945</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:12">
+      <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>21080.76727866939</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>3659.607732467544</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>0.1735993611660674</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>0.8264006388339326</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>3.781357362460543</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97">
         <v>204.5987623370494</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97">
         <v>777.8155627410831</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97">
         <v>2564.834021749035</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97">
         <v>33.82687089245699</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97">
         <v>167.5599260160454</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97">
         <v>655.6806093244622</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:12">
+      <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>17421.15954620184</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>3360.322025718969</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>0.1928873917265505</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>0.8071126082734495</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>3.470661696354207</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98">
         <v>161.0290932380663</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98">
         <v>573.2168004040336</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98">
         <v>1787.018459007952</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J98">
         <v>29.58141122550677</v>
       </c>
-      <c r="K98" t="n">
+      <c r="K98">
         <v>133.7330551235884</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98">
         <v>488.1206833084167</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:12">
+      <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>14060.83752048288</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>3009.445076195057</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>0.2140302860203812</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>0.7859697139796188</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>3.180603754547901</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99">
         <v>123.779629953604</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99">
         <v>412.1877071659674</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99">
         <v>1213.801658603918</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J99">
         <v>25.23103771663505</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99">
         <v>104.1516438980817</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99">
         <v>354.3876281848284</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:12">
+      <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>11051.39244428782</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>2620.666323890309</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>0.2371344911604206</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>0.7628655088395794</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>2.910568762217487</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100">
         <v>92.65432414394016</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100">
         <v>288.4080772123634</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100">
         <v>801.6139514379511</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100">
         <v>20.92527239017706</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100">
         <v>78.92060618144663</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100">
         <v>250.2359842867467</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:12">
+      <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>8430.726120397509</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>2211.328002702248</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>0.2622938962934765</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>0.7377061037065235</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>2.659886945058356</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101">
         <v>67.3169410802421</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101">
         <v>195.7537530684232</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101">
         <v>513.2058742255876</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J101">
         <v>16.81602167856676</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K101">
         <v>57.99533379126957</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101">
         <v>171.3153781053</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:12">
+      <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>6219.39811769526</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>1801.03788958882</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>0.2895839525796807</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>0.7104160474203193</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>2.427842041981545</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102">
         <v>47.29535077880668</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102">
         <v>128.4368119881811</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102">
         <v>317.4521211571644</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J102">
         <v>13.04378534968506</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102">
         <v>41.17931211270281</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102">
         <v>113.3200443140304</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:12">
+      <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>4418.36022810644</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>1409.698828615678</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>0.3190547524052441</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>0.6809452475947559</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>2.213680313081291</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103">
         <v>31.99940586822605</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103">
         <v>81.14146120937447</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103">
         <v>189.0153091689832</v>
       </c>
-      <c r="J103" t="n">
+      <c r="J103">
         <v>9.723392872763597</v>
       </c>
-      <c r="K103" t="n">
+      <c r="K103">
         <v>28.13552676301774</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103">
         <v>72.14073220132764</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:12">
+      <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>3008.661399490763</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>1055.207048640793</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>0.350723098591086</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>0.649276901408914</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>2.016619829765133</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104">
         <v>20.75223176364217</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104">
         <v>49.14205534114841</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104">
         <v>107.8738479596088</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J104">
         <v>6.931701930309464</v>
       </c>
-      <c r="K104" t="n">
+      <c r="K104">
         <v>18.41213389025415</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104">
         <v>44.00520543830989</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:12">
+      <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>1953.454350849969</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>751.2276164020647</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>0.3845636915319763</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>0.6154363084680237</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>1.835859825713971</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105">
         <v>12.83232832077831</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105">
         <v>28.38982357750624</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105">
         <v>58.73179261846036</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J105">
         <v>4.699854809513177</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105">
         <v>11.48043195994468</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105">
         <v>25.59307154805574</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:12">
+      <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>1202.226734447905</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>505.5359762712267</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>0.4204996959274763</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>0.5795003040725237</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>1.670589884498793</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106">
         <v>7.521410257894741</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106">
         <v>15.55749525672792</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106">
         <v>30.34196904095412</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J106">
         <v>3.012143548943371</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106">
         <v>6.780577150431506</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106">
         <v>14.11263958811106</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="107" spans="1:12">
+      <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>696.6907581766779</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>319.358252001969</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107">
         <v>0.4583931224202935</v>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>0.5416068775797065</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>1.519998740763896</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G107">
         <v>4.151104315718287</v>
       </c>
-      <c r="H107" t="n">
+      <c r="H107">
         <v>8.036084998833182</v>
       </c>
-      <c r="I107" t="n">
+      <c r="I107">
         <v>14.7844737842262</v>
       </c>
-      <c r="J107" t="n">
+      <c r="J107">
         <v>1.812226351213773</v>
       </c>
-      <c r="K107" t="n">
+      <c r="K107">
         <v>3.768433601488135</v>
       </c>
-      <c r="L107" t="n">
+      <c r="L107">
         <v>7.332062437679552</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:12">
+      <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>377.3325061747089</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>187.9250482328983</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108">
         <v>0.4980356718747339</v>
       </c>
-      <c r="E108" t="n">
+      <c r="E108">
         <v>0.5019643281252661</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>1.383282474775787</v>
       </c>
-      <c r="G108" t="n">
+      <c r="G108">
         <v>2.141206330422691</v>
       </c>
-      <c r="H108" t="n">
+      <c r="H108">
         <v>3.884980683114895</v>
       </c>
-      <c r="I108" t="n">
+      <c r="I108">
         <v>6.748388785393018</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J108">
         <v>1.01561631751857</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K108">
         <v>1.956207250274362</v>
       </c>
-      <c r="L108" t="n">
+      <c r="L108">
         <v>3.563628836191417</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:12">
+      <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>189.4074579418106</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>102.117313465306</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109">
         <v>0.5391409323315997</v>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>0.4608590676684003</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>1.259651882185864</v>
       </c>
-      <c r="G109" t="n">
+      <c r="G109">
         <v>1.023627806693517</v>
       </c>
-      <c r="H109" t="n">
+      <c r="H109">
         <v>1.743774352692203</v>
       </c>
-      <c r="I109" t="n">
+      <c r="I109">
         <v>2.863408102278124</v>
       </c>
-      <c r="J109" t="n">
+      <c r="J109">
         <v>0.5255996667250409</v>
       </c>
-      <c r="K109" t="n">
+      <c r="K109">
         <v>0.9405909327557924</v>
       </c>
-      <c r="L109" t="n">
+      <c r="L109">
         <v>1.607421585917054</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:12">
+      <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>87.29014447650458</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110">
         <v>50.74517144410657</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110">
         <v>0.5813390703891592</v>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>0.4186609296108408</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>1.148338799167237</v>
       </c>
-      <c r="G110" t="n">
+      <c r="G110">
         <v>0.4492839586973558</v>
       </c>
-      <c r="H110" t="n">
+      <c r="H110">
         <v>0.7201465459986865</v>
       </c>
-      <c r="I110" t="n">
+      <c r="I110">
         <v>1.119633749585921</v>
       </c>
-      <c r="J110" t="n">
+      <c r="J110">
         <v>0.2487488751332212</v>
       </c>
-      <c r="K110" t="n">
+      <c r="K110">
         <v>0.4149912660307516</v>
       </c>
-      <c r="L110" t="n">
+      <c r="L110">
         <v>0.6668306531612617</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:12">
+      <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>36.544973032398</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111">
         <v>22.8104725649766</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111">
         <v>0.6241753837047455</v>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>0.3758246162952545</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>1.048601155044226</v>
       </c>
-      <c r="G111" t="n">
+      <c r="G111">
         <v>0.179140609340451</v>
       </c>
-      <c r="H111" t="n">
+      <c r="H111">
         <v>0.2708625873013307</v>
       </c>
-      <c r="I111" t="n">
+      <c r="I111">
         <v>0.3994872035872343</v>
       </c>
-      <c r="J111" t="n">
+      <c r="J111">
         <v>0.106490627211598</v>
       </c>
-      <c r="K111" t="n">
+      <c r="K111">
         <v>0.1662423908975305</v>
       </c>
-      <c r="L111" t="n">
+      <c r="L111">
         <v>0.25183938713051</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:12">
+      <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>13.73450046742141</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>9.162480626789653</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112">
         <v>0.6671142243959507</v>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>0.3328857756040493</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>0.9597265087426701</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G112">
         <v>0.06411947692216484</v>
       </c>
-      <c r="H112" t="n">
+      <c r="H112">
         <v>0.09172197796087972</v>
       </c>
-      <c r="I112" t="n">
+      <c r="I112">
         <v>0.1286246162859036</v>
       </c>
-      <c r="J112" t="n">
+      <c r="J112">
         <v>0.04073810963390864</v>
       </c>
-      <c r="K112" t="n">
+      <c r="K112">
         <v>0.05975176368593249</v>
       </c>
-      <c r="L112" t="n">
+      <c r="L112">
         <v>0.08559699623297956</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:12">
+      <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>4.572019840631752</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>3.244075717349274</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113">
         <v>0.7095497899022709</v>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>0.2904502100977291</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>0.8810338032872012</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G113">
         <v>0.02032805886339122</v>
       </c>
-      <c r="H113" t="n">
+      <c r="H113">
         <v>0.02760250103871487</v>
       </c>
-      <c r="I113" t="n">
+      <c r="I113">
         <v>0.03690263832502386</v>
       </c>
-      <c r="J113" t="n">
+      <c r="J113">
         <v>0.01373692371013356</v>
       </c>
-      <c r="K113" t="n">
+      <c r="K113">
         <v>0.01901365405202385</v>
       </c>
-      <c r="L113" t="n">
+      <c r="L113">
         <v>0.02584523254704706</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:12">
+      <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>1.327944123282478</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114">
         <v>0.9970536724544408</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114">
         <v>0.7508250196475692</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>0.2491749803524308</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>0.8118730510093036</v>
       </c>
-      <c r="G114" t="n">
+      <c r="G114">
         <v>0.005623132350239033</v>
       </c>
-      <c r="H114" t="n">
+      <c r="H114">
         <v>0.007274442175323642</v>
       </c>
-      <c r="I114" t="n">
+      <c r="I114">
         <v>0.009300137286308989</v>
       </c>
-      <c r="J114" t="n">
+      <c r="J114">
         <v>0.004020941387951527</v>
       </c>
-      <c r="K114" t="n">
+      <c r="K114">
         <v>0.005276730341890288</v>
       </c>
-      <c r="L114" t="n">
+      <c r="L114">
         <v>0.006831578495023214</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:12">
+      <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>0.3308904508280375</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115">
         <v>0.2614892373852673</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115">
         <v>0.7902592435983058</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>0.2097407564016942</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>0.7516226571712508</v>
       </c>
-      <c r="G115" t="n">
+      <c r="G115">
         <v>0.001334422755133266</v>
       </c>
-      <c r="H115" t="n">
+      <c r="H115">
         <v>0.001651309825084609</v>
       </c>
-      <c r="I115" t="n">
+      <c r="I115">
         <v>0.002025695110985348</v>
       </c>
-      <c r="J115" t="n">
+      <c r="J115">
         <v>0.00100432373058284</v>
       </c>
-      <c r="K115" t="n">
+      <c r="K115">
         <v>0.00125578895393876</v>
       </c>
-      <c r="L115" t="n">
+      <c r="L115">
         <v>0.001554848153132925</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:12">
+      <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>0.06940121344277018</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>0.05740758992067914</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116">
         <v>0.8271842389041042</v>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>0.1728157610958958</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>0.6996841314395974</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G116">
         <v>0.0002665550838297942</v>
       </c>
-      <c r="H116" t="n">
+      <c r="H116">
         <v>0.0003168870699513432</v>
       </c>
-      <c r="I116" t="n">
+      <c r="I116">
         <v>0.0003743852859007389</v>
       </c>
-      <c r="J116" t="n">
+      <c r="J116">
         <v>0.0002099906325178743</v>
       </c>
-      <c r="K116" t="n">
+      <c r="K116">
         <v>0.0002514652233559207</v>
       </c>
-      <c r="L116" t="n">
+      <c r="L116">
         <v>0.0002990591991941651</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:12">
+      <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>0.01199362352209104</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>0.01032635349284631</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117">
         <v>0.8609869630997011</v>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>0.1390130369002989</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>0.6554740735064797</v>
       </c>
-      <c r="G117" t="n">
-        <v>4.387135208192971e-05</v>
-      </c>
-      <c r="H117" t="n">
-        <v>5.0331986121549e-05</v>
-      </c>
-      <c r="I117" t="n">
-        <v>5.749821594939561e-05</v>
-      </c>
-      <c r="J117" t="n">
-        <v>3.597396399628419e-05</v>
-      </c>
-      <c r="K117" t="n">
-        <v>4.147459083804642e-05</v>
-      </c>
-      <c r="L117" t="n">
-        <v>4.759397583824445e-05</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
+      <c r="G117">
+        <v>4.387135208192971E-05</v>
+      </c>
+      <c r="H117">
+        <v>5.0331986121549E-05</v>
+      </c>
+      <c r="I117">
+        <v>5.749821594939561E-05</v>
+      </c>
+      <c r="J117">
+        <v>3.597396399628419E-05</v>
+      </c>
+      <c r="K117">
+        <v>4.147459083804642E-05</v>
+      </c>
+      <c r="L117">
+        <v>4.759397583824445E-05</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
+      <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>0.001667270029244735</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>0.001485796950216175</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118">
         <v>0.8911555561814026</v>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>0.1088444438185974</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>0.6184136176953448</v>
       </c>
-      <c r="G118" t="n">
-        <v>5.808276081744093e-06</v>
-      </c>
-      <c r="H118" t="n">
-        <v>6.460634039619294e-06</v>
-      </c>
-      <c r="I118" t="n">
-        <v>7.166229827846611e-06</v>
-      </c>
-      <c r="J118" t="n">
-        <v>4.929597621030281e-06</v>
-      </c>
-      <c r="K118" t="n">
-        <v>5.500626841762222e-06</v>
-      </c>
-      <c r="L118" t="n">
-        <v>6.119385000198026e-06</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
+      <c r="G118">
+        <v>5.808276081744093E-06</v>
+      </c>
+      <c r="H118">
+        <v>6.460634039619294E-06</v>
+      </c>
+      <c r="I118">
+        <v>7.166229827846611E-06</v>
+      </c>
+      <c r="J118">
+        <v>4.929597621030281E-06</v>
+      </c>
+      <c r="K118">
+        <v>5.500626841762222E-06</v>
+      </c>
+      <c r="L118">
+        <v>6.119385000198026E-06</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
+      <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>0.0001814730790285597</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>0.0001664695198096652</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119">
         <v>0.9173234988946578</v>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>0.08267650110534219</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>0.5879160528643574</v>
       </c>
-      <c r="G119" t="n">
-        <v>6.020938853926645e-07</v>
-      </c>
-      <c r="H119" t="n">
-        <v>6.523579578752001e-07</v>
-      </c>
-      <c r="I119" t="n">
-        <v>7.055957882273174e-07</v>
-      </c>
-      <c r="J119" t="n">
-        <v>5.26014161534741e-07</v>
-      </c>
-      <c r="K119" t="n">
-        <v>5.710292207319407e-07</v>
-      </c>
-      <c r="L119" t="n">
-        <v>6.18758158435804e-07</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
+      <c r="G119">
+        <v>6.020938853926645E-07</v>
+      </c>
+      <c r="H119">
+        <v>6.523579578752001E-07</v>
+      </c>
+      <c r="I119">
+        <v>7.055957882273174E-07</v>
+      </c>
+      <c r="J119">
+        <v>5.26014161534741E-07</v>
+      </c>
+      <c r="K119">
+        <v>5.710292207319407E-07</v>
+      </c>
+      <c r="L119">
+        <v>6.18758158435804E-07</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
+      <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" t="n">
-        <v>1.500355921889457e-05</v>
-      </c>
-      <c r="C120" t="n">
-        <v>1.409292574131231e-05</v>
-      </c>
-      <c r="D120" t="n">
+      <c r="B120">
+        <v>1.500355921889457E-05</v>
+      </c>
+      <c r="C120">
+        <v>1.409292574131231E-05</v>
+      </c>
+      <c r="D120">
         <v>0.9393055031611787</v>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>0.06069449683882133</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>0.563374135201238</v>
       </c>
-      <c r="G120" t="n">
-        <v>4.740858645827276e-08</v>
-      </c>
-      <c r="H120" t="n">
-        <v>5.026407248253555e-08</v>
-      </c>
-      <c r="I120" t="n">
-        <v>5.323783035211734e-08</v>
-      </c>
-      <c r="J120" t="n">
-        <v>4.241061538795061e-08</v>
-      </c>
-      <c r="K120" t="n">
-        <v>4.501505919719964e-08</v>
-      </c>
-      <c r="L120" t="n">
-        <v>4.772893770386329e-08</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
+      <c r="G120">
+        <v>4.740858645827276E-08</v>
+      </c>
+      <c r="H120">
+        <v>5.026407248253555E-08</v>
+      </c>
+      <c r="I120">
+        <v>5.323783035211734E-08</v>
+      </c>
+      <c r="J120">
+        <v>4.241061538795061E-08</v>
+      </c>
+      <c r="K120">
+        <v>4.501505919719964E-08</v>
+      </c>
+      <c r="L120">
+        <v>4.772893770386329E-08</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
+      <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" t="n">
-        <v>9.106334775822652e-07</v>
-      </c>
-      <c r="C121" t="n">
-        <v>8.715839944054233e-07</v>
-      </c>
-      <c r="D121" t="n">
+      <c r="B121">
+        <v>9.106334775822652E-07</v>
+      </c>
+      <c r="C121">
+        <v>8.715839944054233E-07</v>
+      </c>
+      <c r="D121">
         <v>0.9571183312077233</v>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>0.04288166879227673</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>0.5441496099643551</v>
       </c>
-      <c r="G121" t="n">
-        <v>2.740419334213928e-09</v>
-      </c>
-      <c r="H121" t="n">
-        <v>2.855486024262784e-09</v>
-      </c>
-      <c r="I121" t="n">
-        <v>2.973757869581788e-09</v>
-      </c>
-      <c r="J121" t="n">
-        <v>2.498005314259252e-09</v>
-      </c>
-      <c r="K121" t="n">
-        <v>2.604443809249033e-09</v>
-      </c>
-      <c r="L121" t="n">
-        <v>2.713878506663651e-09</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
+      <c r="G121">
+        <v>2.740419334213928E-09</v>
+      </c>
+      <c r="H121">
+        <v>2.855486024262784E-09</v>
+      </c>
+      <c r="I121">
+        <v>2.973757869581788E-09</v>
+      </c>
+      <c r="J121">
+        <v>2.498005314259252E-09</v>
+      </c>
+      <c r="K121">
+        <v>2.604443809249033E-09</v>
+      </c>
+      <c r="L121">
+        <v>2.713878506663651E-09</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
+      <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" t="n">
-        <v>3.904948317684185e-08</v>
-      </c>
-      <c r="C122" t="n">
-        <v>3.791629899364383e-08</v>
-      </c>
-      <c r="D122" t="n">
+      <c r="B122">
+        <v>3.904948317684185E-08</v>
+      </c>
+      <c r="C122">
+        <v>3.791629899364383E-08</v>
+      </c>
+      <c r="D122">
         <v>0.9709808148275302</v>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>0.02901918517246982</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>0.5295683728686125</v>
       </c>
-      <c r="G122" t="n">
-        <v>1.11917861182584e-10</v>
-      </c>
-      <c r="H122" t="n">
-        <v>1.150666900488561e-10</v>
-      </c>
-      <c r="I122" t="n">
-        <v>1.182718453190044e-10</v>
-      </c>
-      <c r="J122" t="n">
-        <v>1.03495329566495e-10</v>
-      </c>
-      <c r="K122" t="n">
-        <v>1.064384949897813e-10</v>
-      </c>
-      <c r="L122" t="n">
-        <v>1.094346974146178e-10</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
+      <c r="G122">
+        <v>1.11917861182584E-10</v>
+      </c>
+      <c r="H122">
+        <v>1.150666900488561E-10</v>
+      </c>
+      <c r="I122">
+        <v>1.182718453190044E-10</v>
+      </c>
+      <c r="J122">
+        <v>1.03495329566495E-10</v>
+      </c>
+      <c r="K122">
+        <v>1.064384949897813E-10</v>
+      </c>
+      <c r="L122">
+        <v>1.094346974146178E-10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
+      <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" t="n">
-        <v>1.133184183198019e-09</v>
-      </c>
-      <c r="C123" t="n">
-        <v>1.111982490674401e-09</v>
-      </c>
-      <c r="D123" t="n">
+      <c r="B123">
+        <v>1.133184183198019E-09</v>
+      </c>
+      <c r="C123">
+        <v>1.111982490674401E-09</v>
+      </c>
+      <c r="D123">
         <v>0.9812901619719194</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>0.01870983802808057</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>0.5189249867933473</v>
       </c>
-      <c r="G123" t="n">
-        <v>3.0931096550135e-12</v>
-      </c>
-      <c r="H123" t="n">
-        <v>3.148828866272188e-12</v>
-      </c>
-      <c r="I123" t="n">
-        <v>3.205155270148273e-12</v>
-      </c>
-      <c r="J123" t="n">
-        <v>2.890702927966767e-12</v>
-      </c>
-      <c r="K123" t="n">
-        <v>2.943165423286253e-12</v>
-      </c>
-      <c r="L123" t="n">
-        <v>2.996202424836555e-12</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
+      <c r="G123">
+        <v>3.0931096550135E-12</v>
+      </c>
+      <c r="H123">
+        <v>3.148828866272188E-12</v>
+      </c>
+      <c r="I123">
+        <v>3.205155270148273E-12</v>
+      </c>
+      <c r="J123">
+        <v>2.890702927966767E-12</v>
+      </c>
+      <c r="K123">
+        <v>2.943165423286253E-12</v>
+      </c>
+      <c r="L123">
+        <v>2.996202424836555E-12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" t="n">
-        <v>2.120169252361771e-11</v>
-      </c>
-      <c r="C124" t="n">
-        <v>2.095948418501194e-11</v>
-      </c>
-      <c r="D124" t="n">
+      <c r="B124">
+        <v>2.120169252361771E-11</v>
+      </c>
+      <c r="C124">
+        <v>2.095948418501194E-11</v>
+      </c>
+      <c r="D124">
         <v>0.9885759904151068</v>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>0.0114240095848932</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>0.5114992318449679</v>
       </c>
-      <c r="G124" t="n">
-        <v>5.511579109370929e-14</v>
-      </c>
-      <c r="H124" t="n">
-        <v>5.571921125868718e-14</v>
-      </c>
-      <c r="I124" t="n">
-        <v>5.632640387608507e-14</v>
-      </c>
-      <c r="J124" t="n">
-        <v>5.189156930283407e-14</v>
-      </c>
-      <c r="K124" t="n">
-        <v>5.246249531948609e-14</v>
-      </c>
-      <c r="L124" t="n">
-        <v>5.303700155030216e-14</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
+      <c r="G124">
+        <v>5.511579109370929E-14</v>
+      </c>
+      <c r="H124">
+        <v>5.571921125868718E-14</v>
+      </c>
+      <c r="I124">
+        <v>5.632640387608507E-14</v>
+      </c>
+      <c r="J124">
+        <v>5.189156930283407E-14</v>
+      </c>
+      <c r="K124">
+        <v>5.246249531948609E-14</v>
+      </c>
+      <c r="L124">
+        <v>5.303700155030216E-14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" t="n">
-        <v>2.422083386057672e-13</v>
-      </c>
-      <c r="C125" t="n">
-        <v>2.406191003953305e-13</v>
-      </c>
-      <c r="D125" t="n">
+      <c r="B125">
+        <v>2.422083386057672E-13</v>
+      </c>
+      <c r="C125">
+        <v>2.406191003953305E-13</v>
+      </c>
+      <c r="D125">
         <v>0.9934385487321165</v>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>0.006561451267883545</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>0.5065845760646212</v>
       </c>
-      <c r="G125" t="n">
-        <v>5.996603102223869e-16</v>
-      </c>
-      <c r="H125" t="n">
-        <v>6.034201649778815e-16</v>
-      </c>
-      <c r="I125" t="n">
-        <v>6.071926173978976e-16</v>
-      </c>
-      <c r="J125" t="n">
-        <v>5.673577793519799e-16</v>
-      </c>
-      <c r="K125" t="n">
-        <v>5.709260166520118e-16</v>
-      </c>
-      <c r="L125" t="n">
-        <v>5.745062308160772e-16</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
+      <c r="G125">
+        <v>5.996603102223869E-16</v>
+      </c>
+      <c r="H125">
+        <v>6.034201649778815E-16</v>
+      </c>
+      <c r="I125">
+        <v>6.071926173978976E-16</v>
+      </c>
+      <c r="J125">
+        <v>5.673577793519799E-16</v>
+      </c>
+      <c r="K125">
+        <v>5.709260166520118E-16</v>
+      </c>
+      <c r="L125">
+        <v>5.745062308160772E-16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" t="n">
-        <v>1.589238210436778e-15</v>
-      </c>
-      <c r="C126" t="n">
-        <v>1.583646962613378e-15</v>
-      </c>
-      <c r="D126" t="n">
+      <c r="B126">
+        <v>1.589238210436778E-15</v>
+      </c>
+      <c r="C126">
+        <v>1.583646962613378E-15</v>
+      </c>
+      <c r="D126">
         <v>0.9964818063228775</v>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>0.003518193677122472</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>0.5035243417642672</v>
       </c>
-      <c r="G126" t="n">
-        <v>3.7472780026744e-18</v>
-      </c>
-      <c r="H126" t="n">
-        <v>3.759854755494721e-18</v>
-      </c>
-      <c r="I126" t="n">
-        <v>3.772452420015899e-18</v>
-      </c>
-      <c r="J126" t="n">
-        <v>3.556280336094258e-18</v>
-      </c>
-      <c r="K126" t="n">
-        <v>3.568237300031795e-18</v>
-      </c>
-      <c r="L126" t="n">
-        <v>3.580214164065393e-18</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
+      <c r="G126">
+        <v>3.7472780026744E-18</v>
+      </c>
+      <c r="H126">
+        <v>3.759854755494721E-18</v>
+      </c>
+      <c r="I126">
+        <v>3.772452420015899E-18</v>
+      </c>
+      <c r="J126">
+        <v>3.556280336094258E-18</v>
+      </c>
+      <c r="K126">
+        <v>3.568237300031795E-18</v>
+      </c>
+      <c r="L126">
+        <v>3.580214164065393E-18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" t="n">
-        <v>5.591247823400106e-18</v>
-      </c>
-      <c r="C127" t="n">
-        <v>5.5814848078361e-18</v>
-      </c>
-      <c r="D127" t="n">
+      <c r="B127">
+        <v>5.591247823400106E-18</v>
+      </c>
+      <c r="C127">
+        <v>5.5814848078361E-18</v>
+      </c>
+      <c r="D127">
         <v>0.9982538753651472</v>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>0.001746124634852797</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>0.501747512419413</v>
       </c>
-      <c r="G127" t="n">
-        <v>1.255585692898019e-20</v>
-      </c>
-      <c r="H127" t="n">
-        <v>1.257675282032032e-20</v>
-      </c>
-      <c r="I127" t="n">
-        <v>1.259766452117807e-20</v>
-      </c>
-      <c r="J127" t="n">
-        <v>1.193707889322363e-20</v>
-      </c>
-      <c r="K127" t="n">
-        <v>1.195696393753636e-20</v>
-      </c>
-      <c r="L127" t="n">
-        <v>1.197686403359755e-20</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
+      <c r="G127">
+        <v>1.255585692898019E-20</v>
+      </c>
+      <c r="H127">
+        <v>1.257675282032032E-20</v>
+      </c>
+      <c r="I127">
+        <v>1.259766452117807E-20</v>
+      </c>
+      <c r="J127">
+        <v>1.193707889322363E-20</v>
+      </c>
+      <c r="K127">
+        <v>1.195696393753636E-20</v>
+      </c>
+      <c r="L127">
+        <v>1.197686403359755E-20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128">
         <v>126</v>
       </c>
-      <c r="B128" t="n">
-        <v>9.763015564006006e-21</v>
-      </c>
-      <c r="C128" t="n">
-        <v>9.755258660330479e-21</v>
-      </c>
-      <c r="D128" t="n">
+      <c r="B128">
+        <v>9.763015564006006E-21</v>
+      </c>
+      <c r="C128">
+        <v>9.755258660330479E-21</v>
+      </c>
+      <c r="D128">
         <v>0.9992054807631234</v>
       </c>
-      <c r="E128" t="n">
+      <c r="E128">
         <v>0.0007945192368765674</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>0.5007947797840014</v>
       </c>
-      <c r="G128" t="n">
-        <v>2.088008675750428e-23</v>
-      </c>
-      <c r="H128" t="n">
-        <v>2.089589134012693e-23</v>
-      </c>
-      <c r="I128" t="n">
-        <v>2.091170085775487e-23</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1.986999726372171e-23</v>
-      </c>
-      <c r="K128" t="n">
-        <v>1.988504431273633e-23</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1.990009606118623e-23</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
+      <c r="G128">
+        <v>2.088008675750428E-23</v>
+      </c>
+      <c r="H128">
+        <v>2.089589134012693E-23</v>
+      </c>
+      <c r="I128">
+        <v>2.091170085775487E-23</v>
+      </c>
+      <c r="J128">
+        <v>1.986999726372171E-23</v>
+      </c>
+      <c r="K128">
+        <v>1.988504431273633E-23</v>
+      </c>
+      <c r="L128">
+        <v>1.990009606118623E-23</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129">
         <v>127</v>
       </c>
-      <c r="B129" t="n">
-        <v>7.756903675528103e-24</v>
-      </c>
-      <c r="C129" t="n">
-        <v>7.754360258289561e-24</v>
-      </c>
-      <c r="D129" t="n">
+      <c r="B129">
+        <v>7.756903675528103E-24</v>
+      </c>
+      <c r="C129">
+        <v>7.754360258289561E-24</v>
+      </c>
+      <c r="D129">
         <v>0.999672109214587</v>
       </c>
-      <c r="E129" t="n">
+      <c r="E129">
         <v>0.0003278907854129542</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>0.5003279305430618</v>
       </c>
-      <c r="G129" t="n">
-        <v>1.579964818713221e-26</v>
-      </c>
-      <c r="H129" t="n">
-        <v>1.580458262265408e-26</v>
-      </c>
-      <c r="I129" t="n">
-        <v>1.580951762793274e-26</v>
-      </c>
-      <c r="J129" t="n">
-        <v>1.504235012197989e-26</v>
-      </c>
-      <c r="K129" t="n">
-        <v>1.504704901462487e-26</v>
-      </c>
-      <c r="L129" t="n">
-        <v>1.505174844989538e-26</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
+      <c r="G129">
+        <v>1.579964818713221E-26</v>
+      </c>
+      <c r="H129">
+        <v>1.580458262265408E-26</v>
+      </c>
+      <c r="I129">
+        <v>1.580951762793274E-26</v>
+      </c>
+      <c r="J129">
+        <v>1.504235012197989E-26</v>
+      </c>
+      <c r="K129">
+        <v>1.504704901462487E-26</v>
+      </c>
+      <c r="L129">
+        <v>1.505174844989538E-26</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130">
         <v>128</v>
       </c>
-      <c r="B130" t="n">
-        <v>2.543417238541541e-27</v>
-      </c>
-      <c r="C130" t="n">
-        <v>2.543108842288819e-27</v>
-      </c>
-      <c r="D130" t="n">
+      <c r="B130">
+        <v>2.543417238541541E-27</v>
+      </c>
+      <c r="C130">
+        <v>2.543108842288819E-27</v>
+      </c>
+      <c r="D130">
         <v>0.9998787472821807</v>
       </c>
-      <c r="E130" t="n">
+      <c r="E130">
         <v>0.0001212527178192646</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130">
         <v>0.5001212527178193</v>
       </c>
-      <c r="G130" t="n">
-        <v>4.933865765073465e-30</v>
-      </c>
-      <c r="H130" t="n">
-        <v>4.934435521867151e-30</v>
-      </c>
-      <c r="I130" t="n">
-        <v>4.935005278660838e-30</v>
-      </c>
-      <c r="J130" t="n">
-        <v>4.698350019466757e-30</v>
-      </c>
-      <c r="K130" t="n">
-        <v>4.698892644984553e-30</v>
-      </c>
-      <c r="L130" t="n">
-        <v>4.699435270502349e-30</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="G130">
+        <v>4.933865765073465E-30</v>
+      </c>
+      <c r="H130">
+        <v>4.934435521867151E-30</v>
+      </c>
+      <c r="I130">
+        <v>4.935005278660838E-30</v>
+      </c>
+      <c r="J130">
+        <v>4.698350019466757E-30</v>
+      </c>
+      <c r="K130">
+        <v>4.698892644984553E-30</v>
+      </c>
+      <c r="L130">
+        <v>4.699435270502349E-30</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131">
         <v>129</v>
       </c>
-      <c r="B131" t="n">
-        <v>3.083962527215307e-31</v>
-      </c>
-      <c r="C131" t="n">
-        <v>3.083962527215307e-31</v>
-      </c>
-      <c r="D131" t="n">
+      <c r="B131">
+        <v>3.083962527215307E-31</v>
+      </c>
+      <c r="C131">
+        <v>3.083962527215307E-31</v>
+      </c>
+      <c r="D131">
         <v>1</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E131">
         <v>0</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>0.5</v>
       </c>
-      <c r="G131" t="n">
-        <v>5.697567936862695e-34</v>
-      </c>
-      <c r="H131" t="n">
-        <v>5.697567936862695e-34</v>
-      </c>
-      <c r="I131" t="n">
-        <v>5.697567936862695e-34</v>
-      </c>
-      <c r="J131" t="n">
-        <v>5.426255177964471e-34</v>
-      </c>
-      <c r="K131" t="n">
-        <v>5.426255177964471e-34</v>
-      </c>
-      <c r="L131" t="n">
-        <v>5.426255177964471e-34</v>
+      <c r="G131">
+        <v>5.697567936862695E-34</v>
+      </c>
+      <c r="H131">
+        <v>5.697567936862695E-34</v>
+      </c>
+      <c r="I131">
+        <v>5.697567936862695E-34</v>
+      </c>
+      <c r="J131">
+        <v>5.426255177964471E-34</v>
+      </c>
+      <c r="K131">
+        <v>5.426255177964471E-34</v>
+      </c>
+      <c r="L131">
+        <v>5.426255177964471E-34</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>